--- a/data/trans_orig/IP18A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35972</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>46420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67381</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79573</t>
+          <t>79181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>94604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91415</t>
+          <t>91675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106696</t>
+          <t>107150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177161</t>
+          <t>175958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198929</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46714</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57220</t>
+          <t>56502</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80420</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126988</t>
+          <t>126489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142383</t>
+          <t>142406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133202</t>
+          <t>133192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150690</t>
+          <t>150125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264849</t>
+          <t>264495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288049</t>
+          <t>288767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66340</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>100748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>100856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114979</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192033</t>
+          <t>192368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213006</t>
+          <t>212363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41339</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>62221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26791</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73022</t>
+          <t>72826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98899</t>
+          <t>99638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130235</t>
+          <t>130322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151204</t>
+          <t>150060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137055</t>
+          <t>137698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154515</t>
+          <t>154700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274949</t>
+          <t>274210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300826</t>
+          <t>301022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123195</t>
+          <t>123311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157361</t>
+          <t>156291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>110984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>143305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241130</t>
+          <t>245853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288357</t>
+          <t>292357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440657</t>
+          <t>441727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474823</t>
+          <t>474707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480825</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>512631</t>
+          <t>513030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>933675</t>
+          <t>929675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>980902</t>
+          <t>976179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36275</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>37689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>45492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69295</t>
+          <t>68236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92121</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>107981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107459</t>
+          <t>107666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123637</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204456</t>
+          <t>205515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227516</t>
+          <t>228259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>25972</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41835</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>52957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75975</t>
+          <t>75740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147948</t>
+          <t>147243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163957</t>
+          <t>163811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164768</t>
+          <t>164847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182481</t>
+          <t>181705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318432</t>
+          <t>318667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>342581</t>
+          <t>341450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35631</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>39541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48596</t>
+          <t>48179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71526</t>
+          <t>71329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106969</t>
+          <t>107458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>122528</t>
+          <t>122421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114905</t>
+          <t>116054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131484</t>
+          <t>131584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226669</t>
+          <t>226866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249599</t>
+          <t>250016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40614</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62680</t>
+          <t>62967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53828</t>
+          <t>52874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79043</t>
+          <t>80304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108198</t>
+          <t>109057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139598</t>
+          <t>139311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161664</t>
+          <t>161623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150414</t>
+          <t>151368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170453</t>
+          <t>169918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>298322</t>
+          <t>297463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>327477</t>
+          <t>326216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>121942</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157901</t>
+          <t>157209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>116359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>152330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251680</t>
+          <t>250288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301133</t>
+          <t>300829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505156</t>
+          <t>505848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>541115</t>
+          <t>540966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>558512</t>
+          <t>557485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>593874</t>
+          <t>593456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071739</t>
+          <t>1072043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1121192</t>
+          <t>1122584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>30645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34589</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>55148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92232</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107369</t>
+          <t>107523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104990</t>
+          <t>103152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120114</t>
+          <t>119863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202037</t>
+          <t>203012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223571</t>
+          <t>223930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>44638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61527</t>
+          <t>61019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84872</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148551</t>
+          <t>148565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165562</t>
+          <t>164929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162503</t>
+          <t>162136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180178</t>
+          <t>179866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>317061</t>
+          <t>317099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340406</t>
+          <t>340914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>27904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44800</t>
+          <t>45407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72677</t>
+          <t>73916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103015</t>
+          <t>102999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117279</t>
+          <t>117162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98711</t>
+          <t>98104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115146</t>
+          <t>115607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207874</t>
+          <t>206635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229327</t>
+          <t>228833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>45009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60511</t>
+          <t>60152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87599</t>
+          <t>86972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140862</t>
+          <t>141542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159172</t>
+          <t>158903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137218</t>
+          <t>137330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155028</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>282945</t>
+          <t>283572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310033</t>
+          <t>310392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>106331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137208</t>
+          <t>139069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115814</t>
+          <t>113675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229916</t>
+          <t>231019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>277629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504061</t>
+          <t>502200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535067</t>
+          <t>534938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522158</t>
+          <t>522788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>554105</t>
+          <t>556244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033871</t>
+          <t>1033559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1081272</t>
+          <t>1080169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35914</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25135</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>41439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53576</t>
+          <t>53254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>65653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41350</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51804</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>41699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86784</t>
+          <t>86709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98227</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113645</t>
+          <t>113120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177324</t>
+          <t>177360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196505</t>
+          <t>197811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29131</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22206</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36819</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27715</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20941</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36364</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20856</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35502</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29131</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37322</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92178</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>106791</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87830</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79181</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>94604</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>80043</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>94689</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99866</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>91675</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>107150</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175958</t>
+          <t>175685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198122</t>
+          <t>198038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37528</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29718</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46731</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>30398</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22947</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38864</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23563</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39758</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37528</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>29791</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>46724</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56502</t>
+          <t>56797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80774</t>
+          <t>80431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>142388</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>133185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>150198</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>134955</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>126489</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142406</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>125595</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>141790</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>142388</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>133192</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>150125</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264495</t>
+          <t>264838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288767</t>
+          <t>288472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19260</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33416</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>30759</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23829</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38870</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24524</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39108</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>24,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25455</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18857</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>32940</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>46465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>108341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100380</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114536</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>93818</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85707</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100748</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>85469</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100053</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>75,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>108341</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>100856</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>114939</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192368</t>
+          <t>190642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212363</t>
+          <t>211908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34451</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26247</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43099</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>50768</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42483</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>62221</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40002</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61140</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34451</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26606</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43608</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99638</t>
+          <t>99409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>146855</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>138207</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155059</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>141775</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>130322</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>150060</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>131403</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>152541</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>146855</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137698</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154700</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274210</t>
+          <t>274439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301022</t>
+          <t>302453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>109774</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>143230</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>123311</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>156291</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>122547</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>156306</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>126565</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>110984</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>143305</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245853</t>
+          <t>243041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292357</t>
+          <t>288656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>497449</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>480784</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>514240</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>680</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>458378</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>441727</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>474707</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>441712</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>475471</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>76,65%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>497449</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>480709</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>513030</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>79,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>929675</t>
+          <t>933376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>976179</t>
+          <t>978991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2012 (tasa de respuesta: 98,2%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2012 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28961</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21569</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37143</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28030</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20415</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35731</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20652</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36927</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28961</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21825</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37689</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,92%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45492</t>
+          <t>45900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68236</t>
+          <t>68723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>116394</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>108212</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123786</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>100366</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>92665</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>107981</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>91469</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>107744</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>116394</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>107666</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>123530</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,08%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205515</t>
+          <t>205028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228259</t>
+          <t>227851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145355</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145355</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145355</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>128396</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>128396</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>128396</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145355</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145355</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30505</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23527</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40130</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>33269</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25972</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42540</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24511</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>41871</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>30505</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22919</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39777</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52957</t>
+          <t>52321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>75314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>174119</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>164494</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>181097</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>156514</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>147243</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>163811</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>147912</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>165272</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>174119</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>164847</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>181705</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318667</t>
+          <t>319093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341450</t>
+          <t>342086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>189783</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>189783</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>189783</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31296</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23519</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39329</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27454</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20179</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35142</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20458</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>34944</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>24011</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39541</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48179</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71329</t>
+          <t>70924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>124299</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>116266</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>115146</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107458</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>122421</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107656</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>122142</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124299</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>116054</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131584</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226866</t>
+          <t>227271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250016</t>
+          <t>250013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142600</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142600</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142600</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33934</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54216</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51057</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40655</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>62967</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40788</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61566</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34324</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52874</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80304</t>
+          <t>81990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109057</t>
+          <t>110550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>160804</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>150026</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170308</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151221</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>139311</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161623</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>140712</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161490</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>160804</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>151368</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169918</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297463</t>
+          <t>295970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>324530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204242</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204242</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204242</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202278</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202278</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202278</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204242</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204242</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>118759</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>151405</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>122091</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>157209</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>123450</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>156938</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>134200</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>116359</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>152330</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250288</t>
+          <t>249664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300829</t>
+          <t>300786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>575615</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>558410</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>591056</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>523247</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>505848</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>540966</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>506119</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>539607</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>78,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>575615</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>557485</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>593456</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072043</t>
+          <t>1072086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1122584</t>
+          <t>1123208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>709815</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>709815</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>709815</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>663057</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>663057</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>663057</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>709815</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>709815</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>709815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2016 (tasa de respuesta: 98,26%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2016 (tasa de respuesta: 98,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22329</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15167</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29903</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22040</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15298</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30645</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16072</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30594</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22329</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15476</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32187</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55148</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>113010</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105436</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120172</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>100781</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>92176</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>107523</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>92227</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>106749</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>113010</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>103152</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>119863</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203012</t>
+          <t>203968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223930</t>
+          <t>223817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36982</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29367</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46862</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>36248</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28274</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44638</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>29363</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>45843</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>36982</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28864</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>46594</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61019</t>
+          <t>61272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84834</t>
+          <t>84999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>171748</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>161868</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>179363</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>156955</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148565</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>164929</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>147360</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>163840</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>171748</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>162136</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>179866</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>82,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>317099</t>
+          <t>316934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340914</t>
+          <t>340661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193203</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193203</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193203</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35868</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27579</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44692</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>26308</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19878</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34041</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19885</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33596</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>14,51%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35868</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27904</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>45407</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>51422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73916</t>
+          <t>73672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>107643</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98819</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115932</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>75,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>110732</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>102999</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117162</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103444</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>117155</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>85,49%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>107643</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>98104</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>115607</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>75,01%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>345</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>206635</t>
+          <t>206879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228833</t>
+          <t>229129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143511</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143511</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143511</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137040</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137040</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137040</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143511</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143511</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143511</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>35856</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27222</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46355</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>37533</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29302</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46663</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28400</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46572</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35856</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27528</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45009</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>61162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86972</t>
+          <t>86033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -5764,67 +5764,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>146483</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135984</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155117</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>150672</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141542</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158903</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>141633</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>159805</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>146483</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137330</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154811</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283572</t>
+          <t>284511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310392</t>
+          <t>309382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188205</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>115286</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>148676</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>106331</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>139069</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>104847</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>137562</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>113675</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>147131</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231019</t>
+          <t>231902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277629</t>
+          <t>275777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>538884</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>521243</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>554633</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>519141</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>502200</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>534938</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>503707</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>536422</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,96%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>538884</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>522788</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>556244</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033559</t>
+          <t>1035411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1080169</t>
+          <t>1079286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>967</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>641269</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>641269</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>641269</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3751</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7215</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18017</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14595</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19399</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13303</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9839</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15659</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>31541</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>27014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>34219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12208</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7754</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17478</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5798</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2989</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33185</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37639</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18805</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25986</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60061</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53254</t>
+          <t>47569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65653</t>
+          <t>59699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9349</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5640</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9553</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25806</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20834</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20596</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16683</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23690</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>78,5%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>20913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>43924</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52102</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9143</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1756</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7753</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21149</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16960</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23810</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>24009</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20296</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26293</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,6%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>44663</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>39837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>48637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17290</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32281</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13605</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26560</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>53446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98157</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89441</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104432</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>81085</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73754</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>86709</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>80,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>106550</t>
+          <t>76012</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98745</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113120</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187635</t>
+          <t>174169</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177360</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197811</t>
+          <t>182968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
